--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_27_43.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_27_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2049746.883201498</v>
+        <v>2049962.081721477</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8252068.146678006</v>
+        <v>8249644.678352093</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11325554.71930173</v>
+        <v>11333548.73828869</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5205315.467488502</v>
+        <v>5204853.251820108</v>
       </c>
     </row>
     <row r="11">
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>157.0459045266863</v>
+        <v>152.5445551021959</v>
       </c>
       <c r="K11" t="n">
         <v>220.0898510449805</v>
@@ -8688,7 +8688,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
-        <v>198.3056898744495</v>
+        <v>193.8043404499591</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,16 +8746,16 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>102.8376266666667</v>
+        <v>98.33627724217631</v>
       </c>
       <c r="K12" t="n">
-        <v>120.1810616158684</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>142.1340339220183</v>
+        <v>121.161342836073</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8764,10 +8764,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>105.4730579898399</v>
       </c>
       <c r="Q12" t="n">
-        <v>115.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>105.0132581705354</v>
+        <v>100.511908746045</v>
       </c>
       <c r="L13" t="n">
-        <v>110.8846762812383</v>
+        <v>106.3833268567479</v>
       </c>
       <c r="M13" t="n">
-        <v>114.9257839476051</v>
+        <v>110.4244345231147</v>
       </c>
       <c r="N13" t="n">
-        <v>103.6855444652332</v>
+        <v>99.18419504074281</v>
       </c>
       <c r="O13" t="n">
-        <v>114.4565384518428</v>
+        <v>109.9551890273524</v>
       </c>
       <c r="P13" t="n">
-        <v>113.7280040491476</v>
+        <v>109.2266546246572</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>87.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K14" t="n">
         <v>220.0898510449805</v>
@@ -8925,7 +8925,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8980,19 +8980,19 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J15" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>69.14317436020005</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>48.13403392201832</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
@@ -9001,7 +9001,7 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>64.44186785772997</v>
+        <v>40.61522729765747</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9062,28 +9062,28 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>33.63624132272333</v>
+        <v>33.63624132272334</v>
       </c>
       <c r="K16" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L16" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M16" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N16" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O16" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P16" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q16" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>87.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K17" t="n">
         <v>220.0898510449805</v>
@@ -9162,7 +9162,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J18" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K18" t="n">
         <v>137.841438974359</v>
@@ -9229,10 +9229,10 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>73.43576930785937</v>
       </c>
       <c r="N18" t="n">
-        <v>61.80917252673298</v>
+        <v>37.98253196666053</v>
       </c>
       <c r="O18" t="n">
         <v>142.5962444444444</v>
@@ -9241,7 +9241,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.98177408602152</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,25 +9302,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L19" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M19" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N19" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O19" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P19" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>87.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K20" t="n">
         <v>220.0898510449805</v>
@@ -9399,7 +9399,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9454,28 +9454,28 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J21" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K21" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>44.55437977987418</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>62.64344746917436</v>
       </c>
       <c r="O21" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>64.80459609357553</v>
+        <v>40.61522729765747</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9536,28 +9536,28 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>32.99542143939611</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L22" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M22" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N22" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O22" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P22" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q22" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>95.4567873274482</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K23" t="n">
         <v>220.0898510449805</v>
@@ -9636,7 +9636,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9691,22 +9691,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>10.12574714858493</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J24" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>44.48225885768622</v>
       </c>
       <c r="L24" t="n">
-        <v>44.55437977987418</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>62.64344746917382</v>
       </c>
       <c r="O24" t="n">
         <v>142.5962444444444</v>
@@ -9715,7 +9715,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>45.98177408602152</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9773,28 +9773,28 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>32.99542143939611</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L25" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M25" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N25" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O25" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P25" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.34295837775146</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>87.04590452668629</v>
+        <v>91.64927167527121</v>
       </c>
       <c r="K26" t="n">
         <v>220.0898510449805</v>
@@ -9873,7 +9873,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
-        <v>128.3056898744495</v>
+        <v>132.9090570230344</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,7 +9931,7 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>32.83762666666669</v>
+        <v>37.44099381525162</v>
       </c>
       <c r="K27" t="n">
         <v>137.841438974359</v>
@@ -9946,13 +9946,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>76.8138164971765</v>
       </c>
       <c r="P27" t="n">
-        <v>60.20122894499109</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>45.98177408602152</v>
+        <v>50.58514123460644</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10010,28 +10010,28 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>32.99542143939611</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>35.01325817053538</v>
+        <v>39.6166253191203</v>
       </c>
       <c r="L28" t="n">
-        <v>40.88467628123804</v>
+        <v>45.48804342982321</v>
       </c>
       <c r="M28" t="n">
-        <v>44.92578394760505</v>
+        <v>49.52915109618998</v>
       </c>
       <c r="N28" t="n">
-        <v>33.68554446523319</v>
+        <v>38.28891161381812</v>
       </c>
       <c r="O28" t="n">
-        <v>44.45653845184279</v>
+        <v>49.05990560042771</v>
       </c>
       <c r="P28" t="n">
-        <v>43.72800404914761</v>
+        <v>48.33137119773254</v>
       </c>
       <c r="Q28" t="n">
-        <v>57.50500162944584</v>
+        <v>62.10836877803077</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>44.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K29" t="n">
         <v>220.0898510449805</v>
@@ -10110,7 +10110,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
-        <v>85.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10171,13 +10171,13 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>127.1420055136471</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>1.554379779874182</v>
+        <v>1.210862616663547</v>
       </c>
       <c r="M30" t="n">
-        <v>5.134033922018318</v>
+        <v>35.82676184743079</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -10189,10 +10189,10 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.981774086021517</v>
+        <v>2.638256922810882</v>
       </c>
       <c r="R30" t="n">
-        <v>8.679503963963953</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -10259,16 +10259,16 @@
         <v>138.9257839476051</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.456538451842789</v>
+        <v>1.113021288632154</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.50500162944584</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>44.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K32" t="n">
         <v>220.0898510449805</v>
@@ -10347,7 +10347,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
-        <v>85.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10402,34 +10402,34 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7.780860757030112</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>0.497921811148359</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>5.134033922018318</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>120.3146648978455</v>
       </c>
       <c r="O33" t="n">
-        <v>5.596244444444437</v>
+        <v>5.252727281233803</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.981774086021517</v>
+        <v>2.638256922810882</v>
       </c>
       <c r="R33" t="n">
-        <v>8.679503963963953</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -10490,22 +10490,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.925783947605055</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O34" t="n">
-        <v>1.456538451842789</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P34" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.50500162944584</v>
+        <v>14.16148446623521</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>44.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K35" t="n">
         <v>220.0898510449805</v>
@@ -10584,7 +10584,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
-        <v>85.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10645,28 +10645,28 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>0.497921811148359</v>
       </c>
       <c r="L36" t="n">
-        <v>1.554379779874182</v>
+        <v>1.210862616663547</v>
       </c>
       <c r="M36" t="n">
-        <v>5.134033922018318</v>
+        <v>4.790516758807684</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>54.34964117241175</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>49.96665321475948</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.981774086021517</v>
+        <v>2.638256922810882</v>
       </c>
       <c r="R36" t="n">
-        <v>8.679503963963953</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -10739,10 +10739,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P37" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q37" t="n">
-        <v>14.50500162944584</v>
+        <v>14.16148446623521</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>44.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K38" t="n">
         <v>220.0898510449805</v>
@@ -10821,7 +10821,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
-        <v>85.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10876,34 +10876,34 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>8.885638294939895</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8414389743589936</v>
+        <v>0.497921811148359</v>
       </c>
       <c r="L39" t="n">
-        <v>1.554379779874182</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>4.790516758807684</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444444444</v>
+        <v>49.21757541611692</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.981774086021517</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
-        <v>45.52166981132082</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -10976,10 +10976,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q40" t="n">
-        <v>14.50500162944584</v>
+        <v>14.16148446623521</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -11037,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>68.04590452668629</v>
+        <v>68.24118952270834</v>
       </c>
       <c r="K41" t="n">
         <v>220.0898510449805</v>
@@ -11058,7 +11058,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
-        <v>109.3056898744495</v>
+        <v>109.5009748704715</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>13.83762666666669</v>
+        <v>14.03291166268875</v>
       </c>
       <c r="K42" t="n">
-        <v>24.84143897435899</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>25.55437977987418</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>29.32931891804037</v>
       </c>
       <c r="N42" t="n">
-        <v>104.2573704724725</v>
+        <v>18.53699707935536</v>
       </c>
       <c r="O42" t="n">
-        <v>29.59624444444444</v>
+        <v>116.0977578216513</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>21.1696924103523</v>
       </c>
       <c r="Q42" t="n">
-        <v>26.98177408602152</v>
+        <v>27.17705908204357</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11195,10 +11195,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>13.99542143939611</v>
+        <v>14.19070643541816</v>
       </c>
       <c r="K43" t="n">
-        <v>16.01325817053538</v>
+        <v>16.20854316655743</v>
       </c>
       <c r="L43" t="n">
         <v>134.8846762812383</v>
@@ -11213,10 +11213,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
-        <v>24.72800404914761</v>
+        <v>24.92328904516967</v>
       </c>
       <c r="Q43" t="n">
-        <v>38.50500162944584</v>
+        <v>38.7002866254679</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>358.7338416634806</v>
+        <v>354.2324922389902</v>
       </c>
       <c r="C11" t="n">
-        <v>341.2728917710076</v>
+        <v>336.7715423465172</v>
       </c>
       <c r="D11" t="n">
-        <v>330.683041620683</v>
+        <v>326.1816921961926</v>
       </c>
       <c r="E11" t="n">
-        <v>357.9303700722618</v>
+        <v>353.4290206477714</v>
       </c>
       <c r="F11" t="n">
-        <v>382.8760457417114</v>
+        <v>378.374696317221</v>
       </c>
       <c r="G11" t="n">
-        <v>391.302737515135</v>
+        <v>386.8013880906447</v>
       </c>
       <c r="H11" t="n">
-        <v>315.4748021157671</v>
+        <v>310.9734526912767</v>
       </c>
       <c r="I11" t="n">
-        <v>186.4758895704059</v>
+        <v>181.9745401459155</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>125.8691179411497</v>
+        <v>121.3677685166593</v>
       </c>
       <c r="S11" t="n">
-        <v>185.0200695862453</v>
+        <v>180.518720161755</v>
       </c>
       <c r="T11" t="n">
-        <v>199.0958495641314</v>
+        <v>194.594500139641</v>
       </c>
       <c r="U11" t="n">
-        <v>227.3456529078365</v>
+        <v>222.8443034833461</v>
       </c>
       <c r="V11" t="n">
-        <v>303.7522584701349</v>
+        <v>299.2509090456445</v>
       </c>
       <c r="W11" t="n">
-        <v>325.240968717413</v>
+        <v>320.7396192929226</v>
       </c>
       <c r="X11" t="n">
-        <v>345.731100678469</v>
+        <v>341.2297512539786</v>
       </c>
       <c r="Y11" t="n">
-        <v>362.2379386560536</v>
+        <v>357.7365892315632</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142.5331836498673</v>
+        <v>138.0318342253769</v>
       </c>
       <c r="C12" t="n">
-        <v>148.7084989883157</v>
+        <v>144.2071495638253</v>
       </c>
       <c r="D12" t="n">
-        <v>123.4450655646388</v>
+        <v>118.9437161401484</v>
       </c>
       <c r="E12" t="n">
-        <v>133.6450804554009</v>
+        <v>129.1437310309105</v>
       </c>
       <c r="F12" t="n">
-        <v>121.0692123933839</v>
+        <v>116.5678629688935</v>
       </c>
       <c r="G12" t="n">
-        <v>113.3435171632106</v>
+        <v>108.8421677387202</v>
       </c>
       <c r="H12" t="n">
-        <v>88.23544423649646</v>
+        <v>83.73409481200608</v>
       </c>
       <c r="I12" t="n">
-        <v>65.39663285141508</v>
+        <v>60.89528342692469</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>76.15783415264313</v>
+        <v>71.65648472815275</v>
       </c>
       <c r="S12" t="n">
-        <v>147.6831711038378</v>
+        <v>143.1818216793474</v>
       </c>
       <c r="T12" t="n">
-        <v>176.1647286948216</v>
+        <v>171.6633792703312</v>
       </c>
       <c r="U12" t="n">
-        <v>201.9413820809748</v>
+        <v>197.4400326564844</v>
       </c>
       <c r="V12" t="n">
-        <v>208.8005871494253</v>
+        <v>204.2992377249349</v>
       </c>
       <c r="W12" t="n">
-        <v>227.6949831609196</v>
+        <v>223.1936337364292</v>
       </c>
       <c r="X12" t="n">
-        <v>181.7729852034775</v>
+        <v>177.2716357789871</v>
       </c>
       <c r="Y12" t="n">
-        <v>181.6826957773044</v>
+        <v>177.181346352814</v>
       </c>
     </row>
     <row r="13">
@@ -23373,31 +23373,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155.8319801819373</v>
+        <v>151.3306307574469</v>
       </c>
       <c r="C13" t="n">
-        <v>143.2468210986278</v>
+        <v>138.7454716741374</v>
       </c>
       <c r="D13" t="n">
-        <v>124.6154730182124</v>
+        <v>120.114123593722</v>
       </c>
       <c r="E13" t="n">
-        <v>122.4339626465692</v>
+        <v>117.9326132220788</v>
       </c>
       <c r="F13" t="n">
-        <v>121.4210480229312</v>
+        <v>116.9196985984409</v>
       </c>
       <c r="G13" t="n">
-        <v>143.9909793584588</v>
+        <v>139.4896299339684</v>
       </c>
       <c r="H13" t="n">
-        <v>138.2271725074396</v>
+        <v>133.7258230829492</v>
       </c>
       <c r="I13" t="n">
-        <v>131.4504749272583</v>
+        <v>126.9491255027679</v>
       </c>
       <c r="J13" t="n">
-        <v>69.35918011667277</v>
+        <v>64.85783069218239</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.16204325169439</v>
+        <v>57.660693827204</v>
       </c>
       <c r="R13" t="n">
-        <v>153.2933913771695</v>
+        <v>148.7920419526791</v>
       </c>
       <c r="S13" t="n">
-        <v>200.0165980369723</v>
+        <v>195.5152486124819</v>
       </c>
       <c r="T13" t="n">
-        <v>203.9455894282815</v>
+        <v>199.4442400037911</v>
       </c>
       <c r="U13" t="n">
-        <v>262.3190293564909</v>
+        <v>257.8176799320005</v>
       </c>
       <c r="V13" t="n">
-        <v>228.137643323828</v>
+        <v>223.6362938993376</v>
       </c>
       <c r="W13" t="n">
-        <v>262.522998336591</v>
+        <v>258.0216489121006</v>
       </c>
       <c r="X13" t="n">
-        <v>201.7096553890372</v>
+        <v>197.2083059645468</v>
       </c>
       <c r="Y13" t="n">
-        <v>194.5846533520948</v>
+        <v>190.0833039276044</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,28 +23610,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,28 +23847,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,28 +24084,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,28 +24321,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>288.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>271.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>260.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>287.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>312.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>321.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>245.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>116.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>55.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>115.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>129.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>157.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>233.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>255.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>275.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>292.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,25 +24479,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>72.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>78.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>53.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>63.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>51.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>43.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>18.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6.157834152643133</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>77.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>106.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>131.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>138.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>157.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>111.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>111.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>85.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>73.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>54.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>52.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>51.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>73.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>68.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>61.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>83.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>130.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>133.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>192.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>158.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>192.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>131.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>124.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>245.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C29" t="n">
-        <v>228.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D29" t="n">
-        <v>217.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E29" t="n">
-        <v>244.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F29" t="n">
-        <v>269.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G29" t="n">
-        <v>278.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H29" t="n">
-        <v>202.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I29" t="n">
-        <v>73.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>12.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S29" t="n">
-        <v>72.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T29" t="n">
-        <v>86.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U29" t="n">
-        <v>114.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V29" t="n">
-        <v>190.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W29" t="n">
-        <v>212.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X29" t="n">
-        <v>232.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y29" t="n">
-        <v>249.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="30">
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C30" t="n">
-        <v>35.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D30" t="n">
-        <v>10.44506556463875</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E30" t="n">
-        <v>20.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F30" t="n">
-        <v>8.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3435171632106346</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>34.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T30" t="n">
-        <v>63.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U30" t="n">
-        <v>88.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V30" t="n">
-        <v>95.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W30" t="n">
-        <v>114.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X30" t="n">
-        <v>68.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y30" t="n">
-        <v>68.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C31" t="n">
-        <v>30.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D31" t="n">
-        <v>11.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E31" t="n">
-        <v>9.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F31" t="n">
-        <v>8.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G31" t="n">
-        <v>30.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H31" t="n">
-        <v>25.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I31" t="n">
-        <v>18.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>40.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S31" t="n">
-        <v>87.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T31" t="n">
-        <v>90.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U31" t="n">
-        <v>149.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V31" t="n">
-        <v>115.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W31" t="n">
-        <v>149.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X31" t="n">
-        <v>88.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y31" t="n">
-        <v>81.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>245.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C32" t="n">
-        <v>228.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D32" t="n">
-        <v>217.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E32" t="n">
-        <v>244.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F32" t="n">
-        <v>269.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G32" t="n">
-        <v>278.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H32" t="n">
-        <v>202.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I32" t="n">
-        <v>73.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>12.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S32" t="n">
-        <v>72.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T32" t="n">
-        <v>86.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U32" t="n">
-        <v>114.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V32" t="n">
-        <v>190.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W32" t="n">
-        <v>212.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X32" t="n">
-        <v>232.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y32" t="n">
-        <v>249.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="33">
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C33" t="n">
-        <v>35.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D33" t="n">
-        <v>10.44506556463875</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E33" t="n">
-        <v>20.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F33" t="n">
-        <v>8.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3435171632106346</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>34.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T33" t="n">
-        <v>63.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U33" t="n">
-        <v>88.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V33" t="n">
-        <v>95.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W33" t="n">
-        <v>114.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X33" t="n">
-        <v>68.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y33" t="n">
-        <v>68.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>42.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C34" t="n">
-        <v>30.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D34" t="n">
-        <v>11.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E34" t="n">
-        <v>9.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F34" t="n">
-        <v>8.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G34" t="n">
-        <v>30.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H34" t="n">
-        <v>25.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I34" t="n">
-        <v>18.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>40.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S34" t="n">
-        <v>87.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T34" t="n">
-        <v>90.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U34" t="n">
-        <v>149.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V34" t="n">
-        <v>115.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W34" t="n">
-        <v>149.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X34" t="n">
-        <v>88.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y34" t="n">
-        <v>81.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>245.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C35" t="n">
-        <v>228.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D35" t="n">
-        <v>217.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E35" t="n">
-        <v>244.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F35" t="n">
-        <v>269.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G35" t="n">
-        <v>278.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H35" t="n">
-        <v>202.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I35" t="n">
-        <v>73.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>12.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S35" t="n">
-        <v>72.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T35" t="n">
-        <v>86.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U35" t="n">
-        <v>114.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V35" t="n">
-        <v>190.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W35" t="n">
-        <v>212.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X35" t="n">
-        <v>232.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y35" t="n">
-        <v>249.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C36" t="n">
-        <v>35.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D36" t="n">
-        <v>10.44506556463875</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E36" t="n">
-        <v>20.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F36" t="n">
-        <v>8.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3435171632106346</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>34.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T36" t="n">
-        <v>63.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U36" t="n">
-        <v>88.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V36" t="n">
-        <v>95.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W36" t="n">
-        <v>114.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X36" t="n">
-        <v>68.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y36" t="n">
-        <v>68.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C37" t="n">
-        <v>30.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D37" t="n">
-        <v>11.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E37" t="n">
-        <v>9.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F37" t="n">
-        <v>8.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G37" t="n">
-        <v>30.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H37" t="n">
-        <v>25.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I37" t="n">
-        <v>18.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>40.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S37" t="n">
-        <v>87.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T37" t="n">
-        <v>90.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U37" t="n">
-        <v>149.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V37" t="n">
-        <v>115.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W37" t="n">
-        <v>149.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X37" t="n">
-        <v>88.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y37" t="n">
-        <v>81.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>245.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C38" t="n">
-        <v>228.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D38" t="n">
-        <v>217.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E38" t="n">
-        <v>244.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F38" t="n">
-        <v>269.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G38" t="n">
-        <v>278.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H38" t="n">
-        <v>202.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I38" t="n">
-        <v>73.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>12.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S38" t="n">
-        <v>72.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T38" t="n">
-        <v>86.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U38" t="n">
-        <v>114.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V38" t="n">
-        <v>190.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W38" t="n">
-        <v>212.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X38" t="n">
-        <v>232.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y38" t="n">
-        <v>249.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="39">
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C39" t="n">
-        <v>35.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D39" t="n">
-        <v>10.44506556463875</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E39" t="n">
-        <v>20.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F39" t="n">
-        <v>8.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3435171632106062</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>34.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T39" t="n">
-        <v>63.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U39" t="n">
-        <v>88.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V39" t="n">
-        <v>95.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W39" t="n">
-        <v>114.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X39" t="n">
-        <v>68.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y39" t="n">
-        <v>68.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C40" t="n">
-        <v>30.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D40" t="n">
-        <v>11.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E40" t="n">
-        <v>9.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F40" t="n">
-        <v>8.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G40" t="n">
-        <v>30.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H40" t="n">
-        <v>25.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I40" t="n">
-        <v>18.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>40.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S40" t="n">
-        <v>87.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T40" t="n">
-        <v>90.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U40" t="n">
-        <v>149.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V40" t="n">
-        <v>115.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W40" t="n">
-        <v>149.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X40" t="n">
-        <v>88.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y40" t="n">
-        <v>81.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>269.7338416634806</v>
+        <v>269.9291266595026</v>
       </c>
       <c r="C41" t="n">
-        <v>252.2728917710076</v>
+        <v>252.4681767670296</v>
       </c>
       <c r="D41" t="n">
-        <v>241.683041620683</v>
+        <v>241.878326616705</v>
       </c>
       <c r="E41" t="n">
-        <v>268.9303700722618</v>
+        <v>269.1256550682838</v>
       </c>
       <c r="F41" t="n">
-        <v>293.8760457417114</v>
+        <v>294.0713307377335</v>
       </c>
       <c r="G41" t="n">
-        <v>302.302737515135</v>
+        <v>302.4980225111571</v>
       </c>
       <c r="H41" t="n">
-        <v>226.4748021157671</v>
+        <v>226.6700871117892</v>
       </c>
       <c r="I41" t="n">
-        <v>97.47588957040591</v>
+        <v>97.67117456642796</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>36.86911794114968</v>
+        <v>37.06440293717174</v>
       </c>
       <c r="S41" t="n">
-        <v>96.02006958624534</v>
+        <v>96.21535458226739</v>
       </c>
       <c r="T41" t="n">
-        <v>110.0958495641314</v>
+        <v>110.2911345601534</v>
       </c>
       <c r="U41" t="n">
-        <v>138.3456529078365</v>
+        <v>138.5409379038585</v>
       </c>
       <c r="V41" t="n">
-        <v>214.7522584701349</v>
+        <v>214.947543466157</v>
       </c>
       <c r="W41" t="n">
-        <v>236.240968717413</v>
+        <v>236.4362537134351</v>
       </c>
       <c r="X41" t="n">
-        <v>256.731100678469</v>
+        <v>256.9263856744911</v>
       </c>
       <c r="Y41" t="n">
-        <v>273.2379386560536</v>
+        <v>273.4332236520756</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53.53318364986734</v>
+        <v>53.72846864588939</v>
       </c>
       <c r="C42" t="n">
-        <v>59.70849898831574</v>
+        <v>59.90378398433779</v>
       </c>
       <c r="D42" t="n">
-        <v>34.44506556463875</v>
+        <v>34.64035056066081</v>
       </c>
       <c r="E42" t="n">
-        <v>44.64508045540094</v>
+        <v>44.840365451423</v>
       </c>
       <c r="F42" t="n">
-        <v>32.06921239338388</v>
+        <v>32.26449738940593</v>
       </c>
       <c r="G42" t="n">
-        <v>24.34351716321063</v>
+        <v>24.53880215923269</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>58.68317110383782</v>
+        <v>58.87845609985987</v>
       </c>
       <c r="T42" t="n">
-        <v>87.1647286948216</v>
+        <v>87.36001369084366</v>
       </c>
       <c r="U42" t="n">
-        <v>112.9413820809748</v>
+        <v>113.1366670769969</v>
       </c>
       <c r="V42" t="n">
-        <v>119.8005871494253</v>
+        <v>119.9958721454473</v>
       </c>
       <c r="W42" t="n">
-        <v>138.6949831609196</v>
+        <v>138.8902681569417</v>
       </c>
       <c r="X42" t="n">
-        <v>92.77298520347748</v>
+        <v>92.96827019949953</v>
       </c>
       <c r="Y42" t="n">
-        <v>92.68269577730436</v>
+        <v>92.87798077332641</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66.8319801819373</v>
+        <v>67.02726517795935</v>
       </c>
       <c r="C43" t="n">
-        <v>54.24682109862783</v>
+        <v>54.44210609464989</v>
       </c>
       <c r="D43" t="n">
-        <v>35.61547301821236</v>
+        <v>35.81075801423441</v>
       </c>
       <c r="E43" t="n">
-        <v>33.43396264656917</v>
+        <v>33.62924764259122</v>
       </c>
       <c r="F43" t="n">
-        <v>32.42104802293125</v>
+        <v>32.6163330189533</v>
       </c>
       <c r="G43" t="n">
-        <v>54.99097935845876</v>
+        <v>55.18626435448081</v>
       </c>
       <c r="H43" t="n">
-        <v>49.22717250743958</v>
+        <v>49.42245750346163</v>
       </c>
       <c r="I43" t="n">
-        <v>42.45047492725828</v>
+        <v>42.64575992328034</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>64.29339137716948</v>
+        <v>64.48867637319154</v>
       </c>
       <c r="S43" t="n">
-        <v>111.0165980369723</v>
+        <v>111.2118830329943</v>
       </c>
       <c r="T43" t="n">
-        <v>114.9455894282815</v>
+        <v>115.1408744243035</v>
       </c>
       <c r="U43" t="n">
-        <v>173.3190293564909</v>
+        <v>173.5143143525129</v>
       </c>
       <c r="V43" t="n">
-        <v>139.137643323828</v>
+        <v>139.3329283198501</v>
       </c>
       <c r="W43" t="n">
-        <v>173.522998336591</v>
+        <v>173.7182833326131</v>
       </c>
       <c r="X43" t="n">
-        <v>112.7096553890372</v>
+        <v>112.9049403850592</v>
       </c>
       <c r="Y43" t="n">
-        <v>105.5846533520948</v>
+        <v>105.7799383481168</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>325309.8672090382</v>
+        <v>331279.7368697742</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>417608.4581105883</v>
+        <v>416836.7828070854</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417608.4581105883</v>
+        <v>416836.7828070854</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>417608.4581105883</v>
+        <v>416836.7828070854</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>417608.4581105882</v>
+        <v>416836.7828070854</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>417608.4581105883</v>
+        <v>411936.6968588677</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>465862.6893655827</v>
+        <v>466237.0268886767</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>465862.6893655826</v>
+        <v>466237.0268886767</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>465862.6893655827</v>
+        <v>466237.0268886767</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>465862.6893655826</v>
+        <v>466237.0268886767</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>439709.4093655826</v>
+        <v>439496.6033997175</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>880722.0641208162</v>
+        <v>880722.0641208158</v>
       </c>
       <c r="C2" t="n">
         <v>880722.0641208161</v>
       </c>
       <c r="D2" t="n">
-        <v>880722.0641208161</v>
+        <v>880722.0641208158</v>
       </c>
       <c r="E2" t="n">
-        <v>295204.3224071971</v>
+        <v>306740.3807122814</v>
       </c>
       <c r="F2" t="n">
-        <v>474171.7484954687</v>
+        <v>472591.7301747383</v>
       </c>
       <c r="G2" t="n">
-        <v>474171.7484954686</v>
+        <v>472591.7301747384</v>
       </c>
       <c r="H2" t="n">
-        <v>474171.7484954688</v>
+        <v>472591.7301747383</v>
       </c>
       <c r="I2" t="n">
-        <v>474171.7484954688</v>
+        <v>472591.7301747384</v>
       </c>
       <c r="J2" t="n">
-        <v>474171.7484954684</v>
+        <v>462719.3606671304</v>
       </c>
       <c r="K2" t="n">
-        <v>577385.3741244453</v>
+        <v>578201.0418878022</v>
       </c>
       <c r="L2" t="n">
-        <v>577385.3741244453</v>
+        <v>578201.0418878024</v>
       </c>
       <c r="M2" t="n">
-        <v>577385.3741244451</v>
+        <v>578201.0418878022</v>
       </c>
       <c r="N2" t="n">
-        <v>577385.3741244455</v>
+        <v>578201.0418878023</v>
       </c>
       <c r="O2" t="n">
-        <v>520398.3341244449</v>
+        <v>519934.6377127904</v>
       </c>
       <c r="P2" t="n">
-        <v>231140.9218926097</v>
+        <v>231140.9218926098</v>
       </c>
     </row>
     <row r="3">
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>19200</v>
+        <v>22801.07953959231</v>
       </c>
       <c r="F3" t="n">
-        <v>56000</v>
+        <v>51886.26455374591</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>19200</v>
+        <v>19631.04172738616</v>
       </c>
       <c r="K3" t="n">
-        <v>90400</v>
+        <v>90243.77200318236</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26374,40 +26374,40 @@
         <v>467615.9599317312</v>
       </c>
       <c r="E4" t="n">
-        <v>177973.1328145445</v>
+        <v>183897.8115058019</v>
       </c>
       <c r="F4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="G4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="H4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="I4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="J4" t="n">
-        <v>269948.8600633092</v>
+        <v>264092.5943250213</v>
       </c>
       <c r="K4" t="n">
-        <v>322237.8183648574</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="L4" t="n">
-        <v>322237.8183648575</v>
+        <v>322644.7142125411</v>
       </c>
       <c r="M4" t="n">
-        <v>322237.8183648575</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="N4" t="n">
-        <v>322237.8183648574</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="O4" t="n">
-        <v>293441.8957559178</v>
+        <v>293201.8180331818</v>
       </c>
       <c r="P4" t="n">
-        <v>144745.8284464477</v>
+        <v>144738.4206832074</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2017.656</v>
+        <v>2396.079944767482</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>7902.486</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11517.453</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="L5" t="n">
-        <v>11517.453</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="M5" t="n">
-        <v>11517.453</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="N5" t="n">
-        <v>11517.453</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="O5" t="n">
-        <v>9499.797</v>
+        <v>9483.379585669421</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>379478.504189085</v>
+        <v>379478.5041890846</v>
       </c>
       <c r="C6" t="n">
         <v>379478.5041890849</v>
       </c>
       <c r="D6" t="n">
-        <v>379478.5041890849</v>
+        <v>379478.5041890846</v>
       </c>
       <c r="E6" t="n">
-        <v>96013.53359265263</v>
+        <v>97645.40972211973</v>
       </c>
       <c r="F6" t="n">
-        <v>140320.4024321595</v>
+        <v>143719.5794228125</v>
       </c>
       <c r="G6" t="n">
-        <v>196320.4024321594</v>
+        <v>195605.8439765585</v>
       </c>
       <c r="H6" t="n">
-        <v>196320.4024321595</v>
+        <v>195605.8439765584</v>
       </c>
       <c r="I6" t="n">
-        <v>196320.4024321595</v>
+        <v>195605.8439765585</v>
       </c>
       <c r="J6" t="n">
-        <v>177120.4024321592</v>
+        <v>171480.2390875374</v>
       </c>
       <c r="K6" t="n">
-        <v>153230.1027595878</v>
+        <v>153766.2235276847</v>
       </c>
       <c r="L6" t="n">
-        <v>243630.1027595878</v>
+        <v>244009.9955308673</v>
       </c>
       <c r="M6" t="n">
-        <v>243630.1027595877</v>
+        <v>244009.995530867</v>
       </c>
       <c r="N6" t="n">
-        <v>243630.1027595881</v>
+        <v>244009.9955308672</v>
       </c>
       <c r="O6" t="n">
-        <v>217456.6413685272</v>
+        <v>217249.4400939392</v>
       </c>
       <c r="P6" t="n">
-        <v>86395.09344616201</v>
+        <v>86402.5012094024</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="O2" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>64.85783069218239</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>24.5388021592327</v>
       </c>
       <c r="K2" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,22 +26944,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>64.85783069218239</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>24.5388021592327</v>
       </c>
       <c r="P2" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
     </row>
     <row r="3">
@@ -28012,31 +28012,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="G11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28057,31 +28057,31 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="R11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="S11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="T11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="U11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="V11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="W11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
     </row>
     <row r="12">
@@ -28091,40 +28091,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="K12" t="n">
-        <v>17.66037735849057</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>20.97269108594535</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -28133,34 +28133,34 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="S12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="T12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="U12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="V12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="W12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
     </row>
     <row r="13">
@@ -28170,76 +28170,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="G13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="H13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="J13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="L13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="M13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="N13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="R13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="T13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="U13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="V13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="W13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>28.50134942449039</v>
       </c>
     </row>
     <row r="14">
@@ -28249,31 +28249,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28294,31 +28294,31 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,40 +28328,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>68.69826461415894</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -28370,34 +28370,34 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>69.53253955660027</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,76 +28407,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,31 +28486,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -28531,31 +28531,31 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,31 +28565,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -28598,10 +28598,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>68.69826461415894</v>
       </c>
       <c r="N18" t="n">
-        <v>69.53253955660033</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -28610,31 +28610,31 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,76 +28644,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
-        <v>93.35918011667275</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,31 +28723,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -28768,31 +28768,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,76 +28802,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>68.69826461415894</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>69.16981132075472</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,76 +28881,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,31 +28960,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
-        <v>85.58911719923809</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -29005,31 +29005,31 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,43 +29039,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L24" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>68.69826461415948</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -29084,31 +29084,31 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,76 +29118,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16204325169439</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,31 +29197,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -29242,31 +29242,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,31 +29276,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -29315,37 +29315,37 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>65.78242794726793</v>
       </c>
       <c r="P27" t="n">
-        <v>73.77317846933916</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,76 +29355,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="L28" t="n">
-        <v>94.00000000000024</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="M28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="N28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="O28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="P28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Q28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,31 +29434,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -29479,31 +29479,31 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y29" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="30">
@@ -29513,40 +29513,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>99.52238000000006</v>
+        <v>99.52238</v>
       </c>
       <c r="J30" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K30" t="n">
-        <v>10.69943346071193</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M30" t="n">
-        <v>137</v>
+        <v>106.3072720745875</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
@@ -29558,31 +29558,31 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y30" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J31" t="n">
         <v>126.9954214393961</v>
@@ -29628,40 +29628,40 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="P31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q31" t="n">
-        <v>137</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y31" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="32">
@@ -29671,31 +29671,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -29716,31 +29716,31 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y32" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="33">
@@ -29750,76 +29750,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>91.7415192429699</v>
+        <v>99.52238</v>
       </c>
       <c r="J33" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>11.02704718548784</v>
       </c>
       <c r="O33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y33" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J34" t="n">
         <v>126.9954214393961</v>
@@ -29859,46 +29859,46 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M34" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y34" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="35">
@@ -29908,31 +29908,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -29953,31 +29953,31 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y35" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="36">
@@ -29987,76 +29987,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>99.52238000000006</v>
+        <v>99.52238</v>
       </c>
       <c r="J36" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>88.24660327203269</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>84.00775419957077</v>
       </c>
       <c r="Q36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y36" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J37" t="n">
         <v>126.9954214393961</v>
@@ -30108,34 +30108,34 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y37" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="38">
@@ -30145,31 +30145,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -30190,31 +30190,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y38" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="39">
@@ -30224,76 +30224,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>90.63674170506012</v>
+        <v>99.52238</v>
       </c>
       <c r="J39" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L39" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N39" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>93.37866902832752</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y39" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J40" t="n">
         <v>126.9954214393961</v>
@@ -30345,34 +30345,34 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y40" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="41">
@@ -30382,31 +30382,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="C41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="D41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="E41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="F41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="G41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="H41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="I41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="J41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -30427,31 +30427,31 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="R41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="S41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="T41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="U41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="V41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="W41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="X41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="Y41" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="C42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="D42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="E42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="F42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="G42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30485,52 +30485,52 @@
         <v>99.52238</v>
       </c>
       <c r="J42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="K42" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="N42" t="n">
-        <v>27.0843416108608</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="O42" t="n">
-        <v>113</v>
+        <v>26.49848662279313</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="Q42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="R42" t="n">
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="T42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="U42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="V42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="W42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="X42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="Y42" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
     </row>
     <row r="43">
@@ -30540,34 +30540,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="C43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="D43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="E43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="F43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="G43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="H43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="I43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="J43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="K43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -30582,34 +30582,34 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="Q43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="R43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="S43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="T43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="U43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="V43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="W43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="X43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
       <c r="Y43" t="n">
-        <v>113</v>
+        <v>112.8047150039779</v>
       </c>
     </row>
     <row r="44">
